--- a/healthcare_surveys/028_parent_stress_and_burnout_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/028_parent_stress_and_burnout_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_i_am_not_experiencing_stress'}</t>
+          <t>1_-_i_am_not_experiencing_stress</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '1 - I am not experiencing stress'}</t>
+          <t>1 - I am not experiencing stress</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_slightly_stressed'}</t>
+          <t>2_-_slightly_stressed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2 - Slightly stressed'}</t>
+          <t>2 - Slightly stressed</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_moderately_stressed'}</t>
+          <t>3_-_moderately_stressed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '3 - Moderately stressed'}</t>
+          <t>3 - Moderately stressed</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_high_stress'}</t>
+          <t>4_-_high_stress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '4 - High stress'}</t>
+          <t>4 - High stress</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_exercise'}</t>
+          <t>1_-_exercise</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '1 - Exercise'}</t>
+          <t>1 - Exercise</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_social_support'}</t>
+          <t>2_-_social_support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '2 - Social support'}</t>
+          <t>2 - Social support</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_relaxation_techniques'}</t>
+          <t>3_-_relaxation_techniques</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '3 - Relaxation techniques'}</t>
+          <t>3 - Relaxation techniques</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_mindfulness'}</t>
+          <t>4_-_mindfulness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '4 - Mindfulness'}</t>
+          <t>4 - Mindfulness</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'school_events'}</t>
+          <t>school_events</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'School events'}</t>
+          <t>School events</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'parenting_demands'}</t>
+          <t>parenting_demands</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Parenting demands'}</t>
+          <t>Parenting demands</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'financial_constraints'}</t>
+          <t>financial_constraints</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Financial constraints'}</t>
+          <t>Financial constraints</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_2_hours'}</t>
+          <t>less_than_2_hours</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 2 hours'}</t>
+          <t>Less than 2 hours</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'2-5_hours'}</t>
+          <t>2-5_hours</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '2-5 hours'}</t>
+          <t>2-5 hours</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'6-10_hours'}</t>
+          <t>6-10_hours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '6-10 hours'}</t>
+          <t>6-10 hours</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_10_hours'}</t>
+          <t>more_than_10_hours</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'More than 10 hours'}</t>
+          <t>More than 10 hours</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'spouse_or_partner'}</t>
+          <t>spouse_or_partner</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse or partner'}</t>
+          <t>Spouse or partner</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'parenting_groups'}</t>
+          <t>parenting_groups</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Parenting groups'}</t>
+          <t>Parenting groups</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'mental_health_service_provider'}</t>
+          <t>mental_health_service_provider</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Mental health service provider'}</t>
+          <t>Mental health service provider</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'energized_and_positive'}</t>
+          <t>energized_and_positive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Energized and positive'}</t>
+          <t>Energized and positive</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'calm_and_content'}</t>
+          <t>calm_and_content</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Calm and content'}</t>
+          <t>Calm and content</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'fatigued_and_irritable'}</t>
+          <t>fatigued_and_irritable</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigued and irritable'}</t>
+          <t>Fatigued and irritable</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'frustrated_and_angry'}</t>
+          <t>frustrated_and_angry</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Frustrated and angry'}</t>
+          <t>Frustrated and angry</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'calm_and_content'}</t>
+          <t>calm_and_content</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Calm and content'}</t>
+          <t>Calm and content</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'energized_and_positive'}</t>
+          <t>energized_and_positive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Energized and positive'}</t>
+          <t>Energized and positive</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'fatigued_and_irritable'}</t>
+          <t>fatigued_and_irritable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigued and irritable'}</t>
+          <t>Fatigued and irritable</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'frustrated_and_angry'}</t>
+          <t>frustrated_and_angry</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Frustrated and angry'}</t>
+          <t>Frustrated and angry</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'individual_counseling_services'}</t>
+          <t>individual_counseling_services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Individual counseling services'}</t>
+          <t>Individual counseling services</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'support_groups'}</t>
+          <t>support_groups</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Support groups'}</t>
+          <t>Support groups</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'online_resources'}</t>
+          <t>online_resources</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Online resources'}</t>
+          <t>Online resources</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_once_a_week'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Less than once a week'}</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_times_a_week'}</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': '1-2 times a week'}</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_2_times_a_week'}</t>
+          <t>more_than_2_times_a_week</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'More than 2 times a week'}</t>
+          <t>More than 2 times a week</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'exercise'}</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Exercise'}</t>
+          <t>Exercise</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'relaxation_techniques'}</t>
+          <t>relaxation_techniques</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Relaxation techniques'}</t>
+          <t>Relaxation techniques</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'social_support'}</t>
+          <t>social_support</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Social support'}</t>
+          <t>Social support</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'mindfulness_and_meditation'}</t>
+          <t>mindfulness_and_meditation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Mindfulness and meditation'}</t>
+          <t>Mindfulness and meditation</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'school-based_resources'}</t>
+          <t>school-based_resources</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'School-based resources'}</t>
+          <t>School-based resources</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'workplace-based_resources'}</t>
+          <t>workplace-based_resources</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Workplace-based resources'}</t>
+          <t>Workplace-based resources</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'family_or_partner'}</t>
+          <t>family_or_partner</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Family or partner'}</t>
+          <t>Family or partner</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'mental_health_provider'}</t>
+          <t>mental_health_provider</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Mental health provider'}</t>
+          <t>Mental health provider</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'school_counselor'}</t>
+          <t>school_counselor</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'School counselor'}</t>
+          <t>School counselor</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_time_per_month'}</t>
+          <t>less_than_1_time_per_month</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 time per month'}</t>
+          <t>Less than 1 time per month</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_times_per_month'}</t>
+          <t>1-2_times_per_month</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': '1-2 times per month'}</t>
+          <t>1-2 times per month</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_2_times_per_month'}</t>
+          <t>more_than_2_times_per_month</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'More than 2 times per month'}</t>
+          <t>More than 2 times per month</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'loss_of_interest_in_activities'}</t>
+          <t>loss_of_interest_in_activities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Loss of interest in activities'}</t>
+          <t>Loss of interest in activities</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'irritability'}</t>
+          <t>irritability</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Irritability'}</t>
+          <t>Irritability</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'insomnia'}</t>
+          <t>insomnia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Insomnia'}</t>
+          <t>Insomnia</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'mood_changes'}</t>
+          <t>mood_changes</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Mood changes'}</t>
+          <t>Mood changes</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_time_per_month'}</t>
+          <t>less_than_1_time_per_month</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 time per month'}</t>
+          <t>Less than 1 time per month</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_times_per_month'}</t>
+          <t>1-2_times_per_month</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': '1-2 times per month'}</t>
+          <t>1-2 times per month</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_2_times_per_month'}</t>
+          <t>more_than_2_times_per_month</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'More than 2 times per month'}</t>
+          <t>More than 2 times per month</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'physical_symptoms'}</t>
+          <t>physical_symptoms</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Physical symptoms'}</t>
+          <t>Physical symptoms</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'emotional_symptoms'}</t>
+          <t>emotional_symptoms</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional symptoms'}</t>
+          <t>Emotional symptoms</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'psychological_symptoms'}</t>
+          <t>psychological_symptoms</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'Psychological symptoms'}</t>
+          <t>Psychological symptoms</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
